--- a/results/Overall Summary Spreadsheet.xlsx
+++ b/results/Overall Summary Spreadsheet.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://autuni-my.sharepoint.com/personal/mkh6113_autuni_ac_nz/Documents/01. Papers/09. Dissertation/4.0 Projects/xai-traffic-prediction/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{A2658411-CB57-4561-ABAE-3EEAA1A9B6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7839F373-E4A2-419B-9F7A-57224FDEEB5C}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{A2658411-CB57-4561-ABAE-3EEAA1A9B6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{950EE70A-3409-4732-8E92-80B6BDF32C36}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{474D6C29-51C4-4AF7-B1DC-362806789A32}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{474D6C29-51C4-4AF7-B1DC-362806789A32}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Per_Detector" sheetId="2" r:id="rId2"/>
+    <sheet name="Per_detector update" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="48">
   <si>
     <t>metric</t>
   </si>
@@ -166,13 +167,28 @@
   </si>
   <si>
     <t>new_impr</t>
+  </si>
+  <si>
+    <t>avg_flow_veh_h_base</t>
+  </si>
+  <si>
+    <t>∆ base_llm</t>
+  </si>
+  <si>
+    <t>∆ llm_llmimpr</t>
+  </si>
+  <si>
+    <t>avg_flow_veh_h_llm</t>
+  </si>
+  <si>
+    <t>avg_flow_veh_h_llmimpr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +217,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -259,14 +282,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -289,11 +312,31 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -329,11 +372,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -348,6 +401,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -913,10 +970,10 @@
       <c r="D1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1340,13 +1397,477 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:F20">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939639A9-4D2A-4297-94A6-D215867E2DE6}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1008</v>
+      </c>
+      <c r="C2" s="1">
+        <v>842</v>
+      </c>
+      <c r="D2" s="1">
+        <v>293</v>
+      </c>
+      <c r="E2" s="1">
+        <f>C2-B2</f>
+        <v>-166</v>
+      </c>
+      <c r="F2" s="1">
+        <f>D2-C2</f>
+        <v>-549</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="1">
+        <v>786</v>
+      </c>
+      <c r="C3" s="1">
+        <v>662</v>
+      </c>
+      <c r="D3" s="1">
+        <v>251</v>
+      </c>
+      <c r="E3" s="1">
+        <f t="shared" ref="E3:E20" si="0">C3-B3</f>
+        <v>-124</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" ref="F3:F20" si="1">D3-C3</f>
+        <v>-411</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="1">
+        <v>106</v>
+      </c>
+      <c r="C4" s="1">
+        <v>281</v>
+      </c>
+      <c r="D4" s="1">
+        <v>652</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="0"/>
+        <v>175</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="1"/>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="1">
+        <v>72</v>
+      </c>
+      <c r="C5" s="1">
+        <v>107</v>
+      </c>
+      <c r="D5" s="1">
+        <v>293</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="1"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1">
+        <v>245</v>
+      </c>
+      <c r="D6" s="1">
+        <v>242</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="0"/>
+        <v>234</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="1"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46</v>
+      </c>
+      <c r="C7" s="1">
+        <v>51</v>
+      </c>
+      <c r="D7" s="1">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="1"/>
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1">
+        <v>344</v>
+      </c>
+      <c r="C8" s="1">
+        <v>345</v>
+      </c>
+      <c r="D8" s="1">
+        <v>263</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="1"/>
+        <v>-82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="1">
+        <v>84</v>
+      </c>
+      <c r="C9" s="1">
+        <v>216</v>
+      </c>
+      <c r="D9" s="1">
+        <v>348</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="0"/>
+        <v>132</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" si="1"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>61</v>
+      </c>
+      <c r="D11" s="1">
+        <v>92</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1">
+        <v>23</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1">
+        <v>278</v>
+      </c>
+      <c r="C13" s="1">
+        <v>515</v>
+      </c>
+      <c r="D13" s="1">
+        <v>976</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="0"/>
+        <v>237</v>
+      </c>
+      <c r="F13" s="1">
+        <f t="shared" si="1"/>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1">
+        <v>48</v>
+      </c>
+      <c r="C14" s="1">
+        <v>49</v>
+      </c>
+      <c r="D14" s="1">
+        <v>167</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1">
+        <v>63</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1">
+        <v>64</v>
+      </c>
+      <c r="C16" s="1">
+        <v>129</v>
+      </c>
+      <c r="D16" s="1">
+        <v>448</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="F16" s="1">
+        <f t="shared" si="1"/>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1">
+        <v>52</v>
+      </c>
+      <c r="D17" s="1">
+        <v>158</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F17" s="1">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="1">
+        <v>372</v>
+      </c>
+      <c r="C18" s="1">
+        <v>305</v>
+      </c>
+      <c r="D18" s="1">
+        <v>477</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="0"/>
+        <v>-67</v>
+      </c>
+      <c r="F18" s="1">
+        <f t="shared" si="1"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1">
+        <v>406</v>
+      </c>
+      <c r="C19" s="1">
+        <v>412</v>
+      </c>
+      <c r="D19" s="1">
+        <v>391</v>
+      </c>
+      <c r="E19" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F19" s="1">
+        <f t="shared" si="1"/>
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="1">
+        <v>294</v>
+      </c>
+      <c r="C20" s="1">
+        <v>277</v>
+      </c>
+      <c r="D20" s="1">
+        <v>122</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="0"/>
+        <v>-17</v>
+      </c>
+      <c r="F20" s="1">
+        <f t="shared" si="1"/>
+        <v>-155</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E2:F20">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
